--- a/erp-server/erp-server-file/src/main/resources/excel/tms/cfgLogisticsCostExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/cfgLogisticsCostExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>配置编码</t>
   </si>
@@ -55,6 +55,9 @@
     <t>数大臣字段</t>
   </si>
   <si>
+    <t>数大臣明细字段</t>
+  </si>
+  <si>
     <t>启用状态</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
   </si>
   <si>
     <t>{.targetFieldName}</t>
+  </si>
+  <si>
+    <t>{.targetDetailFieldName}</t>
   </si>
   <si>
     <t>{.disabledName}</t>
@@ -1049,7 +1055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.875" style="1" customWidth="1"/>
@@ -1057,12 +1063,11 @@
     <col min="3" max="3" width="17.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.375" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.75" customWidth="1"/>
-    <col min="8" max="8" width="17.75" customWidth="1"/>
-    <col min="9" max="9" width="16.875" customWidth="1"/>
+    <col min="6" max="8" width="17.75" customWidth="1"/>
+    <col min="9" max="10" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1102,46 +1107,52 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/cfgLogisticsCostExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/cfgLogisticsCostExport.xlsx
@@ -34,7 +34,7 @@
     <t>配置编码</t>
   </si>
   <si>
-    <t>配置单据</t>
+    <t>识别维度</t>
   </si>
   <si>
     <t>配置平台</t>
@@ -76,7 +76,7 @@
     <t>{.code}</t>
   </si>
   <si>
-    <t>{.businessTypeName}</t>
+    <t>{.identifyTypeName}</t>
   </si>
   <si>
     <t>{.dictPlatformName}</t>
